--- a/project/df_fred.xlsx
+++ b/project/df_fred.xlsx
@@ -442,92 +442,92 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>dgs10</t>
+          <t>DGS10</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>fedfunds</t>
+          <t>FEDFUNDS</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>unrate</t>
+          <t>UNRATE</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>indpro</t>
+          <t>INDPRO</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>payems</t>
+          <t>PAYEMS</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>rsafs</t>
+          <t>RSAFS</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>awhman</t>
+          <t>AWHMAN</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>umtmti</t>
+          <t>UMTMTI</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>cpi</t>
+          <t>CPIAUCSL</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>pce</t>
+          <t>PCEPI</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>core_cpi</t>
+          <t>CPILFESL</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>VIXCLS</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>oil</t>
+          <t>DCOILWTICO</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>M2SL</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>houst</t>
+          <t>HOUST</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>umcsent</t>
+          <t>UMCSENT</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>loans</t>
+          <t>LOANS</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>icsa</t>
+          <t>ICSA</t>
         </is>
       </c>
     </row>
